--- a/606-22_ДемьянцевВВ_Лаб5.xlsx
+++ b/606-22_ДемьянцевВВ_Лаб5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vital\OneDrive\Рабочий стол\metrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3325C3D8-92BC-4A38-909D-5FBA30DE68D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEAE662B-8742-4A90-BD76-0DD8060AC4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>ГСЭ</t>
   </si>
@@ -118,6 +118,21 @@
   </si>
   <si>
     <t>Циклы</t>
+  </si>
+  <si>
+    <t>Приемочное число</t>
+  </si>
+  <si>
+    <t>Аттестовано</t>
+  </si>
+  <si>
+    <t>Результат</t>
+  </si>
+  <si>
+    <t>аттестовано</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
@@ -258,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -269,6 +284,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -283,12 +304,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -312,11 +327,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -595,24 +646,28 @@
   <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="3" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
     <col min="20" max="20" width="12.140625" customWidth="1"/>
     <col min="26" max="26" width="11.5703125" customWidth="1"/>
+    <col min="28" max="28" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -638,16 +693,16 @@
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="10" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="1"/>
@@ -675,7 +730,7 @@
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -688,7 +743,7 @@
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -733,15 +788,6 @@
         <v>11</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -819,19 +865,19 @@
       <c r="AC6" s="1"/>
     </row>
     <row r="7" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="12" t="s">
         <v>13</v>
@@ -841,36 +887,36 @@
       <c r="P7" s="12"/>
       <c r="Q7" s="12"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="7" t="s">
+      <c r="S7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="9"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="11"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="12" t="s">
         <v>15</v>
@@ -888,12 +934,12 @@
       <c r="T8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="U8" s="7" t="s">
+      <c r="U8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="9"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="11"/>
       <c r="Y8" s="13" t="s">
         <v>4</v>
       </c>
@@ -905,7 +951,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="2">
         <v>1</v>
       </c>
@@ -1007,23 +1053,23 @@
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="N10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" s="2">
         <v>5</v>
       </c>
       <c r="Q10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" s="1">
         <f ca="1">RAND()</f>
-        <v>0.45256545014266547</v>
+        <v>0.22306240739915351</v>
       </c>
       <c r="S10" s="15"/>
       <c r="T10" s="18"/>
@@ -1081,38 +1127,38 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="2">
         <v>5</v>
       </c>
       <c r="P11" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R11" s="1">
         <f ca="1">RAND()</f>
-        <v>0.10990817802841679</v>
+        <v>0.1144335423859888</v>
       </c>
       <c r="S11" s="2">
         <v>1</v>
       </c>
       <c r="T11" s="2">
         <f>M10</f>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="U11" s="2" t="str">
         <f>IF(N10=5,"B",IF(N10=4,"C",IF(N10=3,"H","")))</f>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="V11" s="3" t="str">
         <f t="shared" ref="V11:X11" si="0">IF(O10=5,"B",IF(O10=4,"C",IF(O10=3,"H","")))</f>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="W11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1120,15 +1166,15 @@
       </c>
       <c r="X11" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="Y11" s="2" cm="1">
         <f t="array" ref="Y11">1-SUMPRODUCT(((U11:X11="H")+(U11:X11=""))*(U$10:X$10))-0.5*SUMPRODUCT((U11:X11="C")*(U$10:X$10))</f>
-        <v>0.40500000000000003</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="Z11" s="2" t="str">
         <f>IF(Y11&gt;=0.5,"Атт.", "Не атт.")</f>
-        <v>Не атт.</v>
+        <v>Атт.</v>
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
@@ -1170,34 +1216,34 @@
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q12" s="2">
         <v>4</v>
       </c>
       <c r="R12" s="1">
         <f ca="1">RAND()</f>
-        <v>0.45999121290348155</v>
+        <v>0.17377140153693171</v>
       </c>
       <c r="S12" s="2">
         <v>2</v>
       </c>
       <c r="T12" s="2">
-        <f t="shared" ref="T11:T26" si="1">M11</f>
-        <v>16</v>
+        <f t="shared" ref="T12:T26" si="1">M11</f>
+        <v>27</v>
       </c>
       <c r="U12" s="3" t="str">
         <f t="shared" ref="U12:U26" si="2">IF(N11=5,"B",IF(N11=4,"C",IF(N11=3,"H","")))</f>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="V12" s="3" t="str">
         <f t="shared" ref="V12:V26" si="3">IF(O11=5,"B",IF(O11=4,"C",IF(O11=3,"H","")))</f>
@@ -1205,19 +1251,19 @@
       </c>
       <c r="W12" s="3" t="str">
         <f t="shared" ref="W12:W26" si="4">IF(P11=5,"B",IF(P11=4,"C",IF(P11=3,"H","")))</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="X12" s="3" t="str">
         <f t="shared" ref="X12:X26" si="5">IF(Q11=5,"B",IF(Q11=4,"C",IF(Q11=3,"H","")))</f>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="Y12" s="4" cm="1">
         <f t="array" ref="Y12">1-SUMPRODUCT(((U12:X12="H")+(U12:X12=""))*(U$10:X$10))-0.5*SUMPRODUCT((U12:X12="C")*(U$10:X$10))</f>
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="Z12" s="3" t="str">
         <f t="shared" ref="Z12:Z26" si="6">IF(Y12&gt;=0.5,"Атт.", "Не атт.")</f>
-        <v>Не атт.</v>
+        <v>Атт.</v>
       </c>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
@@ -1259,42 +1305,42 @@
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="2">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="N13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" s="2">
         <v>5</v>
       </c>
       <c r="Q13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13" s="1">
         <f ca="1">RAND()</f>
-        <v>0.17190785130629371</v>
+        <v>1.2732591834401452E-2</v>
       </c>
       <c r="S13" s="2">
         <v>3</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U13" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="V13" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="W13" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="X13" s="3" t="str">
         <f t="shared" si="5"/>
@@ -1302,11 +1348,11 @@
       </c>
       <c r="Y13" s="4" cm="1">
         <f t="array" ref="Y13">1-SUMPRODUCT(((U13:X13="H")+(U13:X13=""))*(U$10:X$10))-0.5*SUMPRODUCT((U13:X13="C")*(U$10:X$10))</f>
-        <v>0.5</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="Z13" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Атт.</v>
+        <v>Не атт.</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
@@ -1348,38 +1394,38 @@
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="2">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="N14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2">
         <v>5</v>
       </c>
       <c r="P14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14" s="1">
         <f ca="1">RAND()</f>
-        <v>0.34042406402508441</v>
+        <v>0.40980659086810389</v>
       </c>
       <c r="S14" s="2">
         <v>4</v>
       </c>
       <c r="T14" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="U14" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="V14" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="W14" s="3" t="str">
         <f t="shared" si="4"/>
@@ -1387,11 +1433,11 @@
       </c>
       <c r="X14" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="Y14" s="4" cm="1">
         <f t="array" ref="Y14">1-SUMPRODUCT(((U14:X14="H")+(U14:X14=""))*(U$10:X$10))-0.5*SUMPRODUCT((U14:X14="C")*(U$10:X$10))</f>
-        <v>0.48499999999999999</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="Z14" s="3" t="str">
         <f t="shared" si="6"/>
@@ -1437,13 +1483,13 @@
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2">
         <v>5</v>
       </c>
       <c r="O15" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P15" s="2">
         <v>3</v>
@@ -1453,18 +1499,18 @@
       </c>
       <c r="R15" s="1">
         <f ca="1">RAND()</f>
-        <v>0.28905772731018642</v>
+        <v>0.65403397219940984</v>
       </c>
       <c r="S15" s="2">
         <v>5</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="1"/>
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="U15" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="V15" s="3" t="str">
         <f t="shared" si="3"/>
@@ -1472,15 +1518,15 @@
       </c>
       <c r="W15" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="X15" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="Y15" s="4" cm="1">
         <f t="array" ref="Y15">1-SUMPRODUCT(((U15:X15="H")+(U15:X15=""))*(U$10:X$10))-0.5*SUMPRODUCT((U15:X15="C")*(U$10:X$10))</f>
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="Z15" s="3" t="str">
         <f t="shared" si="6"/>
@@ -1526,13 +1572,13 @@
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N16" s="2">
         <v>4</v>
       </c>
       <c r="O16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16" s="2">
         <v>5</v>
@@ -1542,14 +1588,14 @@
       </c>
       <c r="R16" s="1">
         <f ca="1">RAND()</f>
-        <v>0.73458878859241061</v>
+        <v>0.16951844613753853</v>
       </c>
       <c r="S16" s="2">
         <v>6</v>
       </c>
       <c r="T16" s="2">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U16" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1557,7 +1603,7 @@
       </c>
       <c r="V16" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>H</v>
+        <v>B</v>
       </c>
       <c r="W16" s="3" t="str">
         <f t="shared" si="4"/>
@@ -1569,11 +1615,11 @@
       </c>
       <c r="Y16" s="4" cm="1">
         <f t="array" ref="Y16">1-SUMPRODUCT(((U16:X16="H")+(U16:X16=""))*(U$10:X$10))-0.5*SUMPRODUCT((U16:X16="C")*(U$10:X$10))</f>
-        <v>0.35499999999999998</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="Z16" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Не атт.</v>
+        <v>Атт.</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
@@ -1615,10 +1661,10 @@
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2">
         <v>5</v>
@@ -1631,14 +1677,14 @@
       </c>
       <c r="R17" s="1">
         <f ca="1">RAND()</f>
-        <v>0.65168969569964885</v>
+        <v>0.88233812335112916</v>
       </c>
       <c r="S17" s="2">
         <v>7</v>
       </c>
       <c r="T17" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="U17" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1646,7 +1692,7 @@
       </c>
       <c r="V17" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="W17" s="3" t="str">
         <f t="shared" si="4"/>
@@ -1658,7 +1704,7 @@
       </c>
       <c r="Y17" s="4" cm="1">
         <f t="array" ref="Y17">1-SUMPRODUCT(((U17:X17="H")+(U17:X17=""))*(U$10:X$10))-0.5*SUMPRODUCT((U17:X17="C")*(U$10:X$10))</f>
-        <v>0.77500000000000002</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="Z17" s="3" t="str">
         <f t="shared" si="6"/>
@@ -1704,34 +1750,34 @@
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N18" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P18" s="2">
         <v>4</v>
       </c>
       <c r="Q18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R18" s="1">
         <f ca="1">RAND()</f>
-        <v>0.40834579753901168</v>
+        <v>0.52591390050695208</v>
       </c>
       <c r="S18" s="2">
         <v>8</v>
       </c>
       <c r="T18" s="2">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U18" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="V18" s="3" t="str">
         <f t="shared" si="3"/>
@@ -1747,7 +1793,7 @@
       </c>
       <c r="Y18" s="4" cm="1">
         <f t="array" ref="Y18">1-SUMPRODUCT(((U18:X18="H")+(U18:X18=""))*(U$10:X$10))-0.5*SUMPRODUCT((U18:X18="C")*(U$10:X$10))</f>
-        <v>0.89500000000000002</v>
+        <v>0.79</v>
       </c>
       <c r="Z18" s="3" t="str">
         <f t="shared" si="6"/>
@@ -1793,38 +1839,38 @@
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="N19" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2">
         <v>4</v>
       </c>
       <c r="P19" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R19" s="1">
         <f ca="1">RAND()</f>
-        <v>0.41186094853102517</v>
+        <v>0.21806463433881862</v>
       </c>
       <c r="S19" s="2">
         <v>9</v>
       </c>
       <c r="T19" s="2">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U19" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>H</v>
+        <v>B</v>
       </c>
       <c r="V19" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="W19" s="3" t="str">
         <f t="shared" si="4"/>
@@ -1832,15 +1878,15 @@
       </c>
       <c r="X19" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="Y19" s="4" cm="1">
         <f t="array" ref="Y19">1-SUMPRODUCT(((U19:X19="H")+(U19:X19=""))*(U$10:X$10))-0.5*SUMPRODUCT((U19:X19="C")*(U$10:X$10))</f>
-        <v>0.39500000000000002</v>
+        <v>0.63</v>
       </c>
       <c r="Z19" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Не атт.</v>
+        <v>Атт.</v>
       </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
@@ -1882,30 +1928,34 @@
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2">
         <v>4</v>
       </c>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
+      <c r="P20" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>3</v>
+      </c>
       <c r="R20" s="1">
         <f ca="1">RAND()</f>
-        <v>3.5075854884181412E-2</v>
+        <v>0.35938968176854791</v>
       </c>
       <c r="S20" s="2">
         <v>10</v>
       </c>
       <c r="T20" s="2">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="U20" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>B</v>
+        <v>H</v>
       </c>
       <c r="V20" s="3" t="str">
         <f t="shared" si="3"/>
@@ -1913,15 +1963,15 @@
       </c>
       <c r="W20" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="X20" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>H</v>
+        <v>B</v>
       </c>
       <c r="Y20" s="4" cm="1">
         <f t="array" ref="Y20">1-SUMPRODUCT(((U20:X20="H")+(U20:X20=""))*(U$10:X$10))-0.5*SUMPRODUCT((U20:X20="C")*(U$10:X$10))</f>
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="Z20" s="3" t="str">
         <f t="shared" si="6"/>
@@ -1967,34 +2017,34 @@
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N21" s="2">
         <v>4</v>
       </c>
       <c r="O21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P21" s="2">
         <v>5</v>
       </c>
       <c r="Q21" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" s="1">
         <f ca="1">RAND()</f>
-        <v>0.37626260104491549</v>
+        <v>0.96798832443552918</v>
       </c>
       <c r="S21" s="2">
         <v>11</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U21" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>H</v>
+        <v>B</v>
       </c>
       <c r="V21" s="3" t="str">
         <f t="shared" si="3"/>
@@ -2002,19 +2052,19 @@
       </c>
       <c r="W21" s="3" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="X21" s="3" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>H</v>
       </c>
       <c r="Y21" s="4" cm="1">
         <f t="array" ref="Y21">1-SUMPRODUCT(((U21:X21="H")+(U21:X21=""))*(U$10:X$10))-0.5*SUMPRODUCT((U21:X21="C")*(U$10:X$10))</f>
-        <v>0.12</v>
+        <v>0.59</v>
       </c>
       <c r="Z21" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Не атт.</v>
+        <v>Атт.</v>
       </c>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
@@ -2056,30 +2106,30 @@
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" s="2">
         <v>4</v>
       </c>
       <c r="Q22" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" s="1">
         <f ca="1">RAND()</f>
-        <v>3.3693566365977201E-2</v>
+        <v>0.1649981200798617</v>
       </c>
       <c r="S22" s="2">
         <v>12</v>
       </c>
       <c r="T22" s="2">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="U22" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2087,7 +2137,7 @@
       </c>
       <c r="V22" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="W22" s="3" t="str">
         <f t="shared" si="4"/>
@@ -2095,15 +2145,15 @@
       </c>
       <c r="X22" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="Y22" s="4" cm="1">
         <f t="array" ref="Y22">1-SUMPRODUCT(((U22:X22="H")+(U22:X22=""))*(U$10:X$10))-0.5*SUMPRODUCT((U22:X22="C")*(U$10:X$10))</f>
-        <v>0.51</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="Z22" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Атт.</v>
+        <v>Не атт.</v>
       </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
@@ -2145,38 +2195,38 @@
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2">
         <v>5</v>
       </c>
       <c r="O23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P23" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23" s="1">
         <f ca="1">RAND()</f>
-        <v>0.98186054491115426</v>
+        <v>0.34281840210971082</v>
       </c>
       <c r="S23" s="2">
         <v>13</v>
       </c>
       <c r="T23" s="2">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="U23" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="V23" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="W23" s="3" t="str">
         <f t="shared" si="4"/>
@@ -2184,11 +2234,11 @@
       </c>
       <c r="X23" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="Y23" s="4" cm="1">
         <f t="array" ref="Y23">1-SUMPRODUCT(((U23:X23="H")+(U23:X23=""))*(U$10:X$10))-0.5*SUMPRODUCT((U23:X23="C")*(U$10:X$10))</f>
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="Z23" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2234,30 +2284,30 @@
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N24" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O24" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24" s="2">
         <v>5</v>
       </c>
       <c r="Q24" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R24" s="1">
         <f ca="1">RAND()</f>
-        <v>0.71425420992224398</v>
+        <v>0.30178548202226496</v>
       </c>
       <c r="S24" s="2">
         <v>14</v>
       </c>
       <c r="T24" s="2">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="U24" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2265,19 +2315,19 @@
       </c>
       <c r="V24" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="W24" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="X24" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="Y24" s="4" cm="1">
         <f t="array" ref="Y24">1-SUMPRODUCT(((U24:X24="H")+(U24:X24=""))*(U$10:X$10))-0.5*SUMPRODUCT((U24:X24="C")*(U$10:X$10))</f>
-        <v>0.63</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="Z24" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2323,38 +2373,38 @@
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" s="2">
         <v>4</v>
       </c>
       <c r="P25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" s="1">
         <f ca="1">RAND()</f>
-        <v>0.67626171769589527</v>
+        <v>0.76394768720475226</v>
       </c>
       <c r="S25" s="2">
         <v>15</v>
       </c>
       <c r="T25" s="2">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="U25" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="V25" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="W25" s="3" t="str">
         <f>IF(P24=5,"B",IF(P24=4,"C",IF(P24=3,"H","")))</f>
@@ -2362,11 +2412,11 @@
       </c>
       <c r="X25" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>H</v>
+        <v>B</v>
       </c>
       <c r="Y25" s="4" cm="1">
         <f t="array" ref="Y25">1-SUMPRODUCT(((U25:X25="H")+(U25:X25=""))*(U$10:X$10))-0.5*SUMPRODUCT((U25:X25="C")*(U$10:X$10))</f>
-        <v>0.71</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="Z25" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2412,34 +2462,34 @@
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N26" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2">
         <v>5</v>
       </c>
       <c r="P26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="2">
         <v>3</v>
       </c>
       <c r="R26" s="1">
         <f ca="1">RAND()</f>
-        <v>2.6626267575888818E-2</v>
+        <v>0.21355399380405105</v>
       </c>
       <c r="S26" s="2">
         <v>16</v>
       </c>
       <c r="T26" s="2">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="U26" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>H</v>
       </c>
       <c r="V26" s="3" t="str">
         <f t="shared" si="3"/>
@@ -2447,19 +2497,19 @@
       </c>
       <c r="W26" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>H</v>
+        <v>C</v>
       </c>
       <c r="X26" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="Y26" s="4" cm="1">
         <f t="array" ref="Y26">1-SUMPRODUCT(((U26:X26="H")+(U26:X26=""))*(U$10:X$10))-0.5*SUMPRODUCT((U26:X26="C")*(U$10:X$10))</f>
-        <v>0.51500000000000001</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="Z26" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Атт.</v>
+        <v>Не атт.</v>
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
@@ -2501,7 +2551,7 @@
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="N27" s="2">
         <v>4</v>
@@ -2510,20 +2560,18 @@
         <v>5</v>
       </c>
       <c r="P27" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Q27" s="2"/>
       <c r="R27" s="1">
         <f ca="1">RAND()</f>
-        <v>1.8669641518307412E-2</v>
-      </c>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
+        <v>0.13225278252703476</v>
+      </c>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
@@ -2567,29 +2615,29 @@
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N28" s="2">
         <v>5</v>
       </c>
       <c r="O28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P28" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q28" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R28" s="1">
         <f ca="1">RAND()</f>
-        <v>0.76278781607007817</v>
-      </c>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
+        <v>0.11788344489032887</v>
+      </c>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -2633,27 +2681,29 @@
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="N29" s="2">
         <v>4</v>
       </c>
       <c r="O29" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P29" s="2">
         <v>4</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" s="2">
+        <v>4</v>
+      </c>
       <c r="R29" s="1">
         <f ca="1">RAND()</f>
-        <v>0.53398233308626897</v>
-      </c>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
+        <v>0.9483003805499578</v>
+      </c>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
@@ -2697,29 +2747,29 @@
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P30" s="2">
         <v>5</v>
       </c>
       <c r="Q30" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R30" s="1">
         <f ca="1">RAND()</f>
-        <v>0.94741523910178738</v>
-      </c>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
+        <v>8.2513222767051086E-3</v>
+      </c>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
@@ -2763,23 +2813,23 @@
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N31" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2">
         <v>5</v>
       </c>
       <c r="P31" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R31" s="1">
         <f ca="1">RAND()</f>
-        <v>0.25950235165794788</v>
+        <v>0.8554929304314427</v>
       </c>
     </row>
     <row r="32" spans="1:29" ht="15.75" x14ac:dyDescent="0.25">
@@ -2818,7 +2868,7 @@
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N32" s="2">
         <v>4</v>
@@ -2827,14 +2877,14 @@
         <v>5</v>
       </c>
       <c r="P32" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q32" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R32" s="1">
         <f ca="1">RAND()</f>
-        <v>0.58280814865347186</v>
+        <v>0.35925420658572638</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2873,23 +2923,23 @@
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N33" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O33" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P33" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R33" s="1">
         <f ca="1">RAND()</f>
-        <v>0.50218152085808099</v>
+        <v>0.54755467366748112</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2924,23 +2974,23 @@
       <c r="K34" s="2"/>
       <c r="L34" s="1"/>
       <c r="M34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2">
         <v>5</v>
       </c>
       <c r="O34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P34" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q34" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34" s="1">
         <f ca="1">RAND()</f>
-        <v>0.38124554258356858</v>
+        <v>0.86171453182482749</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -2973,23 +3023,23 @@
       <c r="K35" s="2"/>
       <c r="L35" s="1"/>
       <c r="M35" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N35" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O35" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P35" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="2">
         <v>5</v>
       </c>
       <c r="R35" s="1">
         <f ca="1">RAND()</f>
-        <v>3.4250921512371857E-2</v>
+        <v>0.11785510667871912</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3020,23 +3070,23 @@
       <c r="K36" s="2"/>
       <c r="L36" s="1"/>
       <c r="M36" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N36" s="2">
         <v>5</v>
       </c>
       <c r="O36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R36" s="1">
         <f ca="1">RAND()</f>
-        <v>0.54906086499393747</v>
+        <v>0.9161751630663616</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3065,23 +3115,19 @@
       <c r="K37" s="2"/>
       <c r="L37" s="1"/>
       <c r="M37" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N37" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2">
-        <v>3</v>
-      </c>
-      <c r="P37" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
       <c r="R37" s="1">
         <f ca="1">RAND()</f>
-        <v>0.27260925414608461</v>
+        <v>0.19153159012528009</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3108,23 +3154,23 @@
       <c r="K38" s="2"/>
       <c r="L38" s="1"/>
       <c r="M38" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O38" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P38" s="2">
         <v>5</v>
       </c>
       <c r="Q38" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R38" s="1">
         <f ca="1">RAND()</f>
-        <v>0.44308450399110821</v>
+        <v>0.74337877270439545</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -3193,17 +3239,17 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+    <row r="42" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="20">
+        <v>3</v>
+      </c>
+      <c r="C42" s="21"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -3213,10 +3259,15 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
+    <row r="43" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="20">
+        <f>COUNTIF(Z11:Z26,"Атт.")</f>
+        <v>12</v>
+      </c>
+      <c r="C43" s="21"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -3233,10 +3284,15 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
+    <row r="44" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="20">
+        <f>COUNTIF(Z11:Z26,"Не атт.")</f>
+        <v>4</v>
+      </c>
+      <c r="C44" s="21"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -3254,9 +3310,14 @@
       <c r="R44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="A45" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="20">
+        <f>B43/(B43+B44)</f>
+        <v>0.75</v>
+      </c>
+      <c r="C45" s="21"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -3273,10 +3334,15 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
+    <row r="46" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="20" t="str">
+        <f>IF(B43&lt;$B$42,"Группа НЕ аттестована","Группа аттестована")</f>
+        <v>Группа аттестована</v>
+      </c>
+      <c r="C46" s="21"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -3318,11 +3384,6 @@
     <sortCondition descending="1" ref="R10:R38"/>
   </sortState>
   <mergeCells count="17">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A7:K7"/>
     <mergeCell ref="S27:W30"/>
     <mergeCell ref="S7:Z7"/>
     <mergeCell ref="A8:A9"/>
@@ -3335,7 +3396,20 @@
     <mergeCell ref="M7:Q7"/>
     <mergeCell ref="Z8:Z10"/>
     <mergeCell ref="Y8:Y10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A7:K7"/>
   </mergeCells>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$B$43&gt;$B$42</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$B$43&lt;$B$42</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
